--- a/Literature review/Summary.xlsx
+++ b/Literature review/Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sandy\Desktop\GUC\Semester 8\Literature review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sandy\Desktop\GUC\Semester 8\25_BSc_Repo_SandyGeorge\Literature review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE1A967-FBD8-4F9F-8352-6D1EED098B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2CAD59-6EE4-4693-A768-ABDE203E62CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{53B0C59D-D55D-4D7B-8F1A-13A8417F94E7}"/>
+    <workbookView xWindow="9600" yWindow="0" windowWidth="9600" windowHeight="10200" xr2:uid="{53B0C59D-D55D-4D7B-8F1A-13A8417F94E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
+  <futureMetadata name="XLRICHVALUE" count="7">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -48,17 +48,77 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="1">
+  <valueMetadata count="7">
     <bk>
       <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="163">
   <si>
     <t>Paper</t>
   </si>
@@ -231,12 +291,524 @@
   <si>
     <t>SFM, CA, DCM, Goal estimation, Social-LSTM, Social-GAN, Structured LSTM, Static-LSTM, CNN + RMDN, Bidirectional LSTM-MDN), Intention-based approaches (CNN + LSTM, Skeleton-based detection, Stacked LSTM)</t>
   </si>
+  <si>
+    <t>Mahir Gulzar, Yar Muhammad, Naveed Muhammad</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> European Social Fund ( IT Academy programme)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Autonomous driving, road vehicles, roads, trajectory prediction, vehicle safety, human
+ intention and behaviour analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behavior Prediction of Traffic Actors for Intelligent 
+Vehicle using Artificial Intelligence Techniques: A 
+Review </t>
+  </si>
+  <si>
+    <t>intelligent driving; deep learning; intelligent vehicles; vehicle behavior prediction; pedestrian behavior prediction.</t>
+  </si>
+  <si>
+    <t>Suresh Kolekar; Shilpa Gite; Biswajeet Pradhan; Ketan Kotecha</t>
+  </si>
+  <si>
+    <t>Research on Traffic Vehicle Behavior Prediction Method Based on Game Theory and HMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SUMIN ZHANG,YONGSHUAI ZHI, RUI HE ,ANDJIANPING LI</t>
+  </si>
+  <si>
+    <t>State Key Laboratory of Automotive Simulation and Control, Jilin University Baidu Online Network Technology (Beijing) Company, Ltd.</t>
+  </si>
+  <si>
+    <t>Gametheory, GMM-HMM,behavior prediction, traf c car, NGSIM dataset</t>
+  </si>
+  <si>
+    <t>Video action recognition for lane-change
+ classification and prediction of surrounding vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mahdi Biparva, David Fern´ andez-Llorca, Senior, IEEE, Rub´ en Izquierdo, and John K. Tsotsos</t>
+  </si>
+  <si>
+    <t>Video action recognition, Lane change predic
+tion, Surrounding Vehicles, Autonomous Vehicles.</t>
+  </si>
+  <si>
+    <t>Vehicle Behavior Prediction and Generalization Using Imbalanced Learning Techniques</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Theodor Westny, Erik Frisk, and Bjorn Olofsson</t>
+  </si>
+  <si>
+    <t>Conference (2021 IEEE International Intelligent Transportation Systems Conference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Acomprehensive review of vehicle detection using
+ computer vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aymen Fadhil Abbas1, Usman Ullah Sheikh2, Fahad Taha AL-Dhief3, Mohd Norzali Haji Mohd4</t>
+  </si>
+  <si>
+    <t>School of Electrical Engineering, Universiti Teknologi Malaysia, Johor Bahru, Malaysia
+ 4Faculty of Electrical and Electronics Engineering, Universiti Tun Hussein Onn Malaysia, Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Computer vision
+ GMM
+ Intelligent transport system
+ KDE
+ Vehicle detection</t>
+  </si>
+  <si>
+    <t>TELKOMNIKA Telecommunication, Computing, Electronics and Control</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence for Vehicle Behavior
+ Anticipation: Hybrid Approach Based
+ on Maneuver Classification and
+ Trajectory Prediction</t>
+  </si>
+  <si>
+    <t>ABDELMOUDJIB BENTERKI, MOUSSA BOUKHNIFER, VINCENT JUDALET AND CHOUBEILA MAAOUI</t>
+  </si>
+  <si>
+    <t>1Department of Autonomous and Connected Vehicles, Institut VEDECOM, 78000 Versailles, France
+ 2Department of Embedded Systems and Energies for Transport, ESTACA Paris-Saclay, 78180 Montigny-le-Bretonneux, France
+ 3Université de Lorraine, LCOMS, F-57000 Metz, France</t>
+  </si>
+  <si>
+    <t>Artificial intelligence, autonomous vehicle, intention prediction, LSTM, maneuver classification, neural networks, trajectory prediction.</t>
+  </si>
+  <si>
+    <t>Lane Change Prediction With an Echo State
+ Network and Recurrent Neural Network
+ in the Urban Area</t>
+  </si>
+  <si>
+    <t>Karoline Griesbach; Matthias Beggiato; Karl Heinz Hoffmann</t>
+  </si>
+  <si>
+    <t>Echo state network, recurrent neural network, LSTM, lane change prediction, urban area.</t>
+  </si>
+  <si>
+    <t>Modeling Vehicle Interactions via Modified LSTM
+ Models for Trajectory Prediction</t>
+  </si>
+  <si>
+    <t>Journal (IEEE Access)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SHENGZHE DAI,  LI LI AND ZHIHENG LI</t>
+  </si>
+  <si>
+    <t>Department of Automation, Tsinghua University, Beijing  Graduate School at Shenzhen, Tsinghua University, Shenzhen 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Trajectory prediction, vehicle interactions, shortcut connection, long short-term
+ memory (LSTM).</t>
+  </si>
+  <si>
+    <t>CoverNet: Multimodal Behavior Prediction using Trajectory Sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Elena Corina Grigore, Freddy A. Boulton, Oscar Beijbom, and Eric M. Wolff
+ nuTonomy, an Aptiv company</t>
+  </si>
+  <si>
+    <t>CVF</t>
+  </si>
+  <si>
+    <t>Pedestrian and Vehicle Detection in Autonomous Vehicle
+ Perception Systems—A Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Luiz G. Galvao, Maysam Abbod , Tatiana Kalganova, Vasile Palade and MdNazmulHuda</t>
+  </si>
+  <si>
+    <t>Department of Electronic and Electrical Engineering, Brunel University London 
+Centre for Data Science, Coventry University, Priory Road, Coventry</t>
+  </si>
+  <si>
+    <t>MDPI</t>
+  </si>
+  <si>
+    <t>autonomous vehicle; vehicle detection; pedestrian detection; generic object detection;
+ deep learning; traditional technique</t>
+  </si>
+  <si>
+    <t>Use of Social Interaction and Intention to Improve
+ Motion Prediction Within Automated Vehicle
+ Framework: A Review</t>
+  </si>
+  <si>
+    <t>An intelligent Lane-Changing Behavior Prediction and 
+Decision-Making strategy for an Autonomous Vehicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Djamel Eddine Benrachou, Sebastien Glaser, Mohammed Elhenawy, and Andry Rakotonirainy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Queensland
+ University of Technology Australian Research Council (QUT ARC) Linkage
+ and the Motor Accident Insurance Commission (MAIC) Queensland</t>
+  </si>
+  <si>
+    <t>Automated vehicle, social interaction, motion
+ prediction, intention prediction, trajectory prediction.</t>
+  </si>
+  <si>
+    <t>Weida Wang, Tianqi Qie, Chao Yang, Member, IEEE, Wenjie Liu, Changle Xiang, and Kun Huang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Natural Science Foundation of China, and the Beijing Institute of Technology Research Fund Program 
+for Young Scholars. </t>
+  </si>
+  <si>
+    <t>Lane-changing behavior prediction, autonomous 
+vehicle, decision-making, fuzzy inference system, long short-term 
+memory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Research Progress and Prospects of Vehicle Driving Behavior Prediction</t>
+  </si>
+  <si>
+    <t>Journal (sensors)</t>
+  </si>
+  <si>
+    <t>Journal (World Electric Vehicle Journal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Xinghua Hu and Mintanyu Zheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> traffic engineering; intelligent transportation; autonomous vehicle; driving behavior;
+ individual intelligent vehicle; Internet of Vehicles</t>
+  </si>
+  <si>
+    <t>Vehicle Detection: A Review</t>
+  </si>
+  <si>
+    <t>Chaochao Meng, Hong Bao and Yan Ma</t>
+  </si>
+  <si>
+    <t>Beijing Key Laboratory of Information Service Engineering, Beijing Union University</t>
+  </si>
+  <si>
+    <t>IOP Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1University of California, Berkeley
+ 2Korea University
+ 3University of California, Santa Cruz</t>
+  </si>
+  <si>
+    <t>A Scenario-Based Platform for Testing Autonomous Vehicle Behavior Prediction Models in Simulation</t>
+  </si>
+  <si>
+    <t>Francis Indaheng, Edward Kim, Kesav Viswanadha, Jay Shenoy, Jinkyu Kim, Daniel J. Fremont, Sanjit A. Seshia</t>
+  </si>
+  <si>
+    <t>categorizing state-of-the-art literature into a novel
+ taxonomy that incorporates motion prediction methods of the
+ two road user classes i.e. pedestrians and vehicles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A Survey on Motion Prediction of
+ Pedestrians and Vehicles for
+ Autonomous Driving</t>
+  </si>
+  <si>
+    <t>Predicting future behavior of pedestrians and vehicles in complex, dynamic environments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The studies discussed in this work are
+ distinguished on the basis of three dimensions i.e. modelling
+ approach, output type and situational awareness.</t>
+  </si>
+  <si>
+    <t>Constant Velocity (CV), Constant Acceleration (CA), Kalman Filter (KF), Particle Filter, Interactive Multiple Models (IMM).  Dynamic Bayesian Networks (DBN), LSTM, Social Clustering, CNNs, CNN+LSTM hybrids. Combination of CNN (spatial features) + LSTM (temporal features).</t>
+  </si>
+  <si>
+    <t>Computer Science and Information Technology Department, Symbiosis Institute of Technology, Symbiosis International (Deemed) University 
+Symbiosis Centre of Applied AI (SCAAI), Symbiosis International (Deemed) University, 
+Centre for Advanced Modelling and Geospatial Information Systems (CAMGIS), Faculty of Engineering and IT, University of Technology Sydney
+Earth Observation Center, Institute of Climate Change, Universiti Kebangsaan Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> to predict the behavior of 
+pedestrians, and another part is to predict the behavior of 
+surrounding vehicles.</t>
+  </si>
+  <si>
+    <t>This article 
+reviewed various behavior prediction techniques using the 
+latest input representation, AI-based solutions for intelligent 
+vehicles in complex and real-time driving scenarios with 
+their insightful analysis.</t>
+  </si>
+  <si>
+    <t>variables 
+such as the atmosphere, a collection of traffic rules are not 
+explicitly inputted into the prediction model. Domain 
+adaptation and explainable artificial intelligence should also 
+be discussed in the real-world adoption of intelligent 
+vehicles.</t>
+  </si>
+  <si>
+    <t>Preferred Reporting Items for Systematic Reviews and 
+Meta-Analysis (PRISMA) method is used to perform a 
+systematic review</t>
+  </si>
+  <si>
+    <t>difficult to accurately predict the vehicle behavior in the traffic environment full of interaction, ignores the driving intention of the driver.  game theory to analyze the behavior of traf c vehicles
+ is a very effective method. However, at present, there is
+ not a set of mature and perfect prediction framework for
+ this method in motion prediction.</t>
+  </si>
+  <si>
+    <t>an interactive behavior prediction method based
+ on Game theory and Markov model</t>
+  </si>
+  <si>
+    <t>GMM-HMM
+ behavior recognition model</t>
+  </si>
+  <si>
+    <t>To improve the precision and robustness of vehicle behavior prediction, a method based on Game theory and HMM is proposed for vehicle behavior prediction. To well design the drivers driving intent, a revenue function is designed and calibrated to model the drivers driving intent, combined with HMM to predict vehicle future behavior. Useful data is ltered and extracted from the NGSIM Dataset to train the GMM-HMM model and revenue function to obtain their parameters. Two sets of experiments are designed to demonstrate the feasibility of our proposed method.</t>
+  </si>
+  <si>
+    <t>Journal (IEEE TRANSACTIONS ON INTELLIGENT VEHICLES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-Stream Convolutional Networks (TS) Two-Stream Inflated 3D Convolutional Networks (I3D) 
+- Spatiotemporal Multiplier Networks (ST) 
+- SlowFast Networks (SF) </t>
+  </si>
+  <si>
+    <t>Lane-change prediction of surrounding vehicles in highway scenarios. Existing systems focus more on the ego-vehicle's lane changes, not surrounding vehicles. Predicting surrounding vehicles' lane changes is harder due to limited sensor information and higher uncertainty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Develop early prediction methods to anticipate lane changes of surrounding vehicles. Use visual action recognition approaches. Evaluate the effect of different observation horizons and context sizes. Create models that can work in highway driving conditions. </t>
+  </si>
+  <si>
+    <t>Use the PREVENTION dataset for training and evaluation</t>
+  </si>
+  <si>
+    <t>Data Augmentation, Multi-Sensor Fusion, Address GPU Limitations, Generalization Across Datasets,Real-Time Deployment, Robustness to Lighting and Weather Conditions, Explicit Turn Signal and Brake Light Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Behavior modeling,  Imbalanced learning,  Generalization study</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> presented an interaction-aware vehicle-intention
+ prediction model consisting of an LSTM autoencoder and
+ SVM classifier. Model performance is enhanced by using the
+ proposed multiclass balancing ensemble method that offers
+ systematic use of the full data set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimating the probability distribution of a discrete set of predefined actions, lane-keeping (LK), lane-change left (LCL), and lane-change right (LCR) over an extended prediction horizon. </t>
+  </si>
+  <si>
+    <t>interaction-aware vehicle-intention prediction model that integrates an LSTM (Long Short-Term Memory) autoencoder with a Support Vector Machine (SVM) classifier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> provide a compre
+hensive review of the various techniques, particularly those in vehicle detection, that could be available for
+ video-based traffic surveillance from a computer vision perspective.</t>
+  </si>
+  <si>
+    <t>A crucial part of ITS involves vehicle detection, with much work being done on the topic, but there
+ are still challenges facing the effective detection of vehicles from the front or rear, illumination and shad
+ows affecting the detection of vehicles and occlusion issues. Many recent studies have attempted to develop
+ appearance-based techniques to detect vehicles just from still images.</t>
+  </si>
+  <si>
+    <t>As a future direction for further research on this topic of vehicle detection,
+ most researchers will focus on detecting vehicles under occlusion and detection of the front and rear view of
+ the vehicle under poor lighting conditions while removing the shadow from the scene.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background Subtraction Techniques  
+- Kernel Density Estimation (KDE)  
+- Codebook Model  
+- Visual Background Extractor (ViBe)  
+- Frame Averaging  
+- Single Gaussian Model  
+- Sigma-Delta Background Estimation  
+- Gaussian Mixture Model (GMM)  
+- Kalman Filter Background Modeling  
+- Eigenbackground Modeling  
+- Optical Flow  
+- Haar-like Features  
+- SIFT (Scale-Invariant Feature Transform)  
+SURF (Speeded Up Robust Features) HOG (Histogram of Oriented Gradients)  </t>
+  </si>
+  <si>
+    <t>Physics-based motion models
+Maneuver-based motion models
+Interaction-aware motion models
+Maneuver classification using Artificial Neural Networks (ANN)
+Trajectory prediction using Long Short-Term Memory (LSTM networks
+Bayesian Networks
+Hidden Markov Models (HMM)
+Support Vector Machine (SVM)
+Random Forests
+Convolutional Neural Networks (CNN)
+Kalman Filter (KF)
+Dynamic Bayesian Networks
+Interactive Multiple Model Trajectory Prediction</t>
+  </si>
+  <si>
+    <t>Develop a framework for trajectory prediction based on ANN and deep LSTM Recurrent Neural Networks from an autonomous vehicle
+Predict vehicle future locations using past location sequences combined with maneuver classification results
+Focus specifically on lane change intention prediction in highway traffic scenarios
+Use ANN to classify vehicle maneuvers into: left lane change, right lane change, lane keeping
+Achieve accurate long-term vehicle trajectory predictions (up to 5 seconds)</t>
+  </si>
+  <si>
+    <t>Propose a hybrid model that combines maneuver classification (ANN) and trajectory prediction (LSTM)
+Evaluate NGSIM-trained model with real on-board sensor data collected from a real test vehicle (VEDECOM demonstrator)
+Demonstrate that combining maneuver classification with trajectory prediction achieves better accuracy than standalone approaches
+Show that ANN-based classification accurately identifies lane changes 2.2 seconds before they happen
+Achieve lateral position prediction error of 0.30 meters and longitudinal position error of 3.1 meters</t>
+  </si>
+  <si>
+    <t>Incorporate driver behavior data for more accurate predictions
+Increase dataset size to improve robustness and generalization
+Extend the approach to urban driving scenes, where traffic is more complex
+Consider interactions with other vehicles and road users when predicting vehicle trajectories
+Explore prediction models that handle occlusion and incomplete data in real-world driving scenarios</t>
+  </si>
+  <si>
+    <t>Current vehicle behavior prediction methods struggle with:
+Short prediction horizons
+Low accuracy in complex scenarios like lane changes
+Ignoring driver intentions and behavior
+Limited ability to predict interactions between vehicles</t>
+  </si>
+  <si>
+    <t>Echo State Network (ESN)
+Recurrent Neural Network (RNN) with Long Short-Term Memory (LSTM) cells
+Moving sum window technique for post-processing prediction output
+10-fold cross-validation
+Standardization of input variables
+CAN-bus-Logger data extraction</t>
+  </si>
+  <si>
+    <t>Lane change prediction in urban areas is more complicated than on highways due to complex traffic rules and the presence of pedestrians, cyclists, cars, and public transportation.</t>
+  </si>
+  <si>
+    <t>Compare the performance of Echo State Network (ESN) and Recurrent Neural Network (RNN) in predicting lane changes.
+Use steering angle and indicator data as inputs for both networks.
+Predict left and right lane changes in urban areas.</t>
+  </si>
+  <si>
+    <t>Spatio-temporal LSTM-based trajectory prediction model (ST-LSTM).
+Structural-RNN (S-RNN) concept applied to traffic scenarios.
+Shortcut connections between input and output of consecutive LSTM layers to address gradient vanishment.
+Safe distance modeling using a formula combining velocity, response time, and braking deceleration.
+10-fold cross-validation for training.
+Oversampling and downsampling techniques to handle imbalanced datasets.
+Adam optimizer for training.
+Mean Squared Error (MSE) as the loss function.
+RMS prediction error for performance evaluation.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Existing LSTM models </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cannot simultaneously describe spatial interactions between vehicles and temporal relations within trajectory time series.</t>
+    </r>
+  </si>
+  <si>
+    <t>Future work should evaluate ST-LSTM on more complex scenarios with larger datasets.</t>
+  </si>
+  <si>
+    <t>Develop a spatio-temporal LSTM-based model (ST-LSTM) for long-term vehicle trajectory prediction in dense traffic.
+Ensure the model can handle both temporal relations within vehicle trajectories and spatial interactions between vehicles.
+Introduce shortcut connections to handle vanishing gradients during long-term trajectory prediction training.
+Achieve higher trajectory prediction accuracy than state-of-the-art models (specifically Maneuver-LSTM (M-LSTM)).
+Train and evaluate the model on NGSIM I-80 and US-101 datasets.</t>
+  </si>
+  <si>
+    <t>wide range of agent preferences (cautious vs. aggressive) and intents (turn vs. go straight).
+Most existing approaches struggle with mode collapse, where multimodal regression degenerates into predicting a single mode.
+Many state-of-the-art methods produce unconstrained, physically infeasible trajectories.
+Existing approaches often do not guarantee coverage of all feasible trajectories within a prediction horizon, which is essential for effective prediction in urban driving.
+Comparing results across trajectory prediction methods is difficult due to a lack of standard public datasets and benchmarks.</t>
+  </si>
+  <si>
+    <t>CoverNet: A method that frames trajectory prediction as classification over a set of candidate trajectories.</t>
+  </si>
+  <si>
+    <t>Although CoverNet performed well, the authors acknowledge that larger, more diverse datasets are needed to fully validate the method across all urban driving scenarios.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Introduce the concept of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trajectory sets for multimodal trajectory prediction, framing the prediction problem as classification over a set of trajectories.</t>
+    </r>
+  </si>
+  <si>
+    <t>Develop a method to generate both fixed and dynamic trajectory sets, ensuring coverage guarantees and eliminating dynamically infeasible trajectories.</t>
+  </si>
+  <si>
+    <t>Autonomous Vehicles (AVs) must accurately perceive their environment to navigate safely, especially in busy urban scenarios.</t>
+  </si>
+  <si>
+    <t>CNN (Convolutional Neural Networks)
+RNN (Recurrent Neural Networks)
+LSTM (Long Short-Term Memory)
+Faster R-CNN
+YOLO (You Only Look Once)
+SSD (Single Shot Multibox Detector)
+Feature Pyramid Networks (FPN)
+Region Proposal Networks (RPN)
+Ensemble Networks
+Encoder-Decoder Networks</t>
+  </si>
+  <si>
+    <t>Reviews both pedestrian and vehicle detection techniques (unlike prior works that focused on only one).
+Covers generic object detection techniques that form the basis of pedestrian and vehicle detection systems.
+Focuses more on deep learning techniques, recognizing their dominance in recent years.
+Summarizes studies from 2012 to 2021, providing comprehensive coverage.
+Includes detection performance comparisons across multiple datasets (Caltech, KITTI, BDD100K, etc.).
+Provides detailed tables that summarize techniques, problems, datasets, and results for both pedestrian and vehicle detection algorithms.</t>
+  </si>
+  <si>
+    <t>Review both pedestrian and vehicle detection algorithms used in AV perception systems, rather than focusing on one type of object detection.
+Provide an overview of traditional and deep learning techniques for detecting pedestrians and vehicles in AV environments.</t>
+  </si>
+  <si>
+    <t>Conduct more research using ensemble techniques, which have shown promising results.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +834,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -271,7 +849,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -294,11 +872,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -314,6 +903,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -379,9 +980,33 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <rv s="0">
     <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -399,6 +1024,12 @@
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
 </richValueRels>
 </file>
 
@@ -719,45 +1350,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B043358F-3CC4-4C6D-88D3-7B2F9EE9F923}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.90625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="85.1796875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="6.6328125" style="3" customWidth="1"/>
     <col min="4" max="4" width="80.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.36328125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="30.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -806,7 +1437,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="154" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="98" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -853,7 +1484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="196" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="98" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -898,7 +1529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="294" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="168" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -943,7 +1574,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="364" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="154" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -978,7 +1609,9 @@
       <c r="L6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N6" s="1" t="s">
         <v>49</v>
       </c>
@@ -986,243 +1619,685 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+    <row r="7" spans="1:15" ht="224" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+    <row r="8" spans="1:15" ht="140" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J8" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O8" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+    <row r="9" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+    <row r="10" spans="1:15" ht="126" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="1" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O10" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
+    <row r="11" spans="1:15" ht="140" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="1" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+    <row r="12" spans="1:15" ht="350" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O12" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+    <row r="13" spans="1:15" ht="378" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J13" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O13" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+    <row r="14" spans="1:15" ht="210" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="K14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+    <row r="15" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O15" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+    <row r="16" spans="1:15" ht="154" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+    <row r="17" spans="1:15" ht="70" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O17" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+    <row r="18" spans="1:15" ht="70" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="O18" s="1">
+        <v>2.5</v>
+      </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+    <row r="19" spans="1:15" ht="70" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="O19" s="1">
+        <v>3.5</v>
+      </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+    <row r="20" spans="1:15" ht="70" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+      <c r="O20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="28" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="42" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
